--- a/artfynd/A 6195-2026 artfynd.xlsx
+++ b/artfynd/A 6195-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -923,6 +923,116 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>131745131</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57892</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>102977</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Gröngöling</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Picus viridis</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>A 6195, Svartsmörjegölen, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>578805</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6406323</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>2 aspar med hackspettshål, trol gröngöling.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 6195-2026 artfynd.xlsx
+++ b/artfynd/A 6195-2026 artfynd.xlsx
@@ -928,7 +928,7 @@
         <v>131745131</v>
       </c>
       <c r="B4" t="n">
-        <v>57892</v>
+        <v>57893</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 6195-2026 artfynd.xlsx
+++ b/artfynd/A 6195-2026 artfynd.xlsx
@@ -928,7 +928,7 @@
         <v>131745131</v>
       </c>
       <c r="B4" t="n">
-        <v>57893</v>
+        <v>57896</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 6195-2026 artfynd.xlsx
+++ b/artfynd/A 6195-2026 artfynd.xlsx
@@ -928,7 +928,7 @@
         <v>131745131</v>
       </c>
       <c r="B4" t="n">
-        <v>57896</v>
+        <v>57898</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 6195-2026 artfynd.xlsx
+++ b/artfynd/A 6195-2026 artfynd.xlsx
@@ -1151,7 +1151,7 @@
         <v>134375536</v>
       </c>
       <c r="B6" t="n">
-        <v>99085</v>
+        <v>99092</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
         <v>134375556</v>
       </c>
       <c r="B7" t="n">
-        <v>99085</v>
+        <v>99092</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 6195-2026 artfynd.xlsx
+++ b/artfynd/A 6195-2026 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>101539539</v>
+        <v>134375432</v>
       </c>
       <c r="B2" t="n">
-        <v>96237</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57269</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,49 +686,49 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220093</v>
+        <v>100038</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Nynäs göl, Svartsmörja, Sm</t>
+          <t>A 6195, Svartsmörjegölen, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>578810.1280209539</v>
+        <v>578762</v>
       </c>
       <c r="R2" t="n">
-        <v>6406344.700274099</v>
+        <v>6406322</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,22 +752,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-06-08</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-06-08</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,7 +766,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -793,72 +777,63 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Eddy Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>101539113</v>
+        <v>134375413</v>
       </c>
       <c r="B3" t="n">
-        <v>96237</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57988</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220093</v>
+        <v>100048</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>bo, hörda ungar</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Nynäs göl, Svartsmörja, Sm</t>
+          <t>A 6195, Svartsmörjegölen, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>578770.2346124807</v>
+        <v>578762</v>
       </c>
       <c r="R3" t="n">
-        <v>6406335.92159932</v>
+        <v>6406322</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -882,22 +857,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-06-08</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-06-08</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Bo ca 3 m upp i klen död asp</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,7 +876,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -918,7 +887,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Eddy Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -928,7 +897,7 @@
         <v>131745131</v>
       </c>
       <c r="B4" t="n">
-        <v>57942</v>
+        <v>57969</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1035,32 +1004,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134375423</v>
+        <v>101539113</v>
       </c>
       <c r="B5" t="n">
-        <v>57988</v>
+        <v>99022</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100048</v>
+        <v>220093</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1068,31 +1037,27 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>föda åt ungar</t>
-        </is>
-      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 6195, Svartsmörjegölen, Sm</t>
+          <t>Nynäs göl, Svartsmörja, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>578762</v>
+        <v>578770</v>
       </c>
       <c r="R5" t="n">
-        <v>6406322</v>
+        <v>6406336</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1116,12 +1081,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2022-06-08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2022-06-08</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1130,6 +1095,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1141,17 +1107,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Eddy Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134375536</v>
+        <v>101539539</v>
       </c>
       <c r="B6" t="n">
-        <v>99092</v>
+        <v>99022</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1178,27 +1144,27 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A 6195, Svartsmörjegölen, Sm</t>
+          <t>Nynäs göl, Svartsmörja, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>578786</v>
+        <v>578810</v>
       </c>
       <c r="R6" t="n">
-        <v>6406385</v>
+        <v>6406345</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1225,12 +1191,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2022-06-08</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2022-06-08</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1251,17 +1217,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Eddy Kasselstrand</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134375556</v>
+        <v>134375536</v>
       </c>
       <c r="B7" t="n">
-        <v>99092</v>
+        <v>99099</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1288,7 +1254,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
@@ -1305,10 +1271,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>578808</v>
+        <v>578786</v>
       </c>
       <c r="R7" t="n">
-        <v>6406387</v>
+        <v>6406385</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1368,10 +1334,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134375432</v>
+        <v>134375556</v>
       </c>
       <c r="B8" t="n">
-        <v>57269</v>
+        <v>99099</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1379,21 +1345,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100038</v>
+        <v>220093</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1401,13 +1367,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1415,13 +1381,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>578762</v>
+        <v>578808</v>
       </c>
       <c r="R8" t="n">
-        <v>6406322</v>
+        <v>6406387</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1459,6 +1425,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
